--- a/site/assets/downloads/SmartCommunications_Program_Scoping_Template.xlsx
+++ b/site/assets/downloads/SmartCommunications_Program_Scoping_Template.xlsx
@@ -331,8 +331,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E9DDFC"/>
-          <bgColor rgb="00E9DDFC"/>
+          <fgColor rgb="00D9C9F7"/>
+          <bgColor rgb="00D9C9F7"/>
         </patternFill>
       </fill>
     </dxf>
